--- a/app/translations.xlsx
+++ b/app/translations.xlsx
@@ -11943,7 +11943,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C492" authorId="0">
+    <comment ref="C494" authorId="0">
       <text>
         <r>
           <rPr>
@@ -11963,7 +11963,7 @@
 </file>
 
 <file path=xl\sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15283" uniqueCount="4179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15345" uniqueCount="4182">
   <si>
     <t>Key</t>
   </si>
@@ -23949,6 +23949,18 @@
     <t>Hard</t>
   </si>
   <si>
+    <t>extracted_text_title</t>
+  </si>
+  <si>
+    <t>Extracted Text from Files</t>
+  </si>
+  <si>
+    <t>copied_to_clipboard</t>
+  </si>
+  <si>
+    <t>Copied to clipboard</t>
+  </si>
+  <si>
     <t>ai_copy_summary</t>
   </si>
   <si>
@@ -23964,9 +23976,6 @@
     <t>ai_copied</t>
   </si>
   <si>
-    <t>Copied to clipboard</t>
-  </si>
-  <si>
     <t>ai_show_answer</t>
   </si>
   <si>
@@ -24312,7 +24321,7 @@
     <t>ai_action_summary_desc</t>
   </si>
   <si>
-    <t>Tóm tắt 1 câu + đoạn chi tiết</t>
+    <t>1-sentence + detailed paragraph</t>
   </si>
   <si>
     <t>ai_action_bullet</t>
@@ -24321,7 +24330,7 @@
     <t>ai_action_bullet_desc</t>
   </si>
   <si>
-    <t>Xem những ý chính quan trọng</t>
+    <t>View important key points</t>
   </si>
   <si>
     <t>ai_action_questions</t>
@@ -24333,7 +24342,7 @@
     <t>ai_action_questions_desc</t>
   </si>
   <si>
-    <t>5-10 câu hỏi tự luận kèm đáp án</t>
+    <t>5-10 essay questions with answers</t>
   </si>
   <si>
     <t>ai_action_mcq</t>
@@ -24345,7 +24354,7 @@
     <t>ai_action_mcq_desc</t>
   </si>
   <si>
-    <t>Các câu hỏi trắc nghiệm nhiều độ khó</t>
+    <t>Multiple choice questions with difficulty levels</t>
   </si>
   <si>
     <t>ai_action_file</t>
@@ -24357,7 +24366,7 @@
     <t>ai_action_file_desc</t>
   </si>
   <si>
-    <t>Ảnh, audio, PDF, DOCX, …</t>
+    <t>Image, audio, PDF, DOCX, …</t>
   </si>
   <si>
     <t>ai_user_id_label</t>
@@ -24369,7 +24378,7 @@
     <t>ai_user_id_desc</t>
   </si>
   <si>
-    <t>ID này dùng để đồng bộ lịch sử AI giữa frontend và backend. Bạn có thể nhập username/email hoặc dùng ID tự tạo.</t>
+    <t>This ID is used to sync AI history between frontend and backend. You can enter username/email or use auto-generated ID.</t>
   </si>
   <si>
     <t>ai_user_id_hint</t>
@@ -24513,7 +24522,7 @@
     <t>ai_raw_text_desc</t>
   </si>
   <si>
-    <t>Text đã được AI xử lý (OCR, transcription, spell check)</t>
+    <t>Text processed by AI (OCR, transcription, spell check)</t>
   </si>
   <si>
     <t>ai_copy_raw_text</t>
@@ -28688,14 +28697,14 @@
     <sheet name="Translations" r:id="rId3" sheetId="1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="true">Translations!$A$1:$AF$493</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="true">Translations!$A$1:$AF$495</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE493"/>
+  <dimension ref="A1:AE495"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="50"/>
   <cols>
     <col min="1" max="1" width="40.0" customWidth="true"/>
@@ -66330,7 +66339,7 @@
         <v>32</v>
       </c>
       <c r="C397" t="s" s="1">
-        <v>3981</v>
+        <v>3975</v>
       </c>
       <c r="D397" t="s" s="2">
         <v>61</v>
@@ -66419,13 +66428,13 @@
     </row>
     <row r="398">
       <c r="A398" t="s" s="1">
-        <v>3982</v>
+        <v>3981</v>
       </c>
       <c r="B398" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C398" t="s" s="1">
-        <v>3983</v>
+        <v>3982</v>
       </c>
       <c r="D398" t="s" s="2">
         <v>61</v>
@@ -66514,13 +66523,13 @@
     </row>
     <row r="399">
       <c r="A399" t="s" s="1">
-        <v>3984</v>
+        <v>3983</v>
       </c>
       <c r="B399" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C399" t="s" s="1">
-        <v>3985</v>
+        <v>3984</v>
       </c>
       <c r="D399" t="s" s="2">
         <v>61</v>
@@ -66609,13 +66618,13 @@
     </row>
     <row r="400">
       <c r="A400" t="s" s="1">
-        <v>3986</v>
+        <v>3985</v>
       </c>
       <c r="B400" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C400" t="s" s="1">
-        <v>3987</v>
+        <v>3986</v>
       </c>
       <c r="D400" t="s" s="2">
         <v>61</v>
@@ -66704,13 +66713,13 @@
     </row>
     <row r="401">
       <c r="A401" t="s" s="1">
-        <v>3988</v>
+        <v>3987</v>
       </c>
       <c r="B401" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C401" t="s" s="1">
-        <v>3989</v>
+        <v>3988</v>
       </c>
       <c r="D401" t="s" s="2">
         <v>61</v>
@@ -66799,13 +66808,13 @@
     </row>
     <row r="402">
       <c r="A402" t="s" s="1">
-        <v>3990</v>
+        <v>3989</v>
       </c>
       <c r="B402" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C402" t="s" s="1">
-        <v>3991</v>
+        <v>3990</v>
       </c>
       <c r="D402" t="s" s="2">
         <v>61</v>
@@ -66894,13 +66903,13 @@
     </row>
     <row r="403">
       <c r="A403" t="s" s="1">
-        <v>3992</v>
+        <v>3991</v>
       </c>
       <c r="B403" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C403" t="s" s="1">
-        <v>3993</v>
+        <v>3992</v>
       </c>
       <c r="D403" t="s" s="2">
         <v>61</v>
@@ -66989,13 +66998,13 @@
     </row>
     <row r="404">
       <c r="A404" t="s" s="1">
-        <v>3994</v>
+        <v>3993</v>
       </c>
       <c r="B404" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C404" t="s" s="1">
-        <v>3995</v>
+        <v>3994</v>
       </c>
       <c r="D404" t="s" s="2">
         <v>61</v>
@@ -67084,13 +67093,13 @@
     </row>
     <row r="405">
       <c r="A405" t="s" s="1">
-        <v>3996</v>
+        <v>3995</v>
       </c>
       <c r="B405" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C405" t="s" s="1">
-        <v>3997</v>
+        <v>3996</v>
       </c>
       <c r="D405" t="s" s="2">
         <v>61</v>
@@ -67179,13 +67188,13 @@
     </row>
     <row r="406">
       <c r="A406" t="s" s="1">
-        <v>3998</v>
+        <v>3997</v>
       </c>
       <c r="B406" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C406" t="s" s="1">
-        <v>3999</v>
+        <v>3998</v>
       </c>
       <c r="D406" t="s" s="2">
         <v>61</v>
@@ -67274,13 +67283,13 @@
     </row>
     <row r="407">
       <c r="A407" t="s" s="1">
-        <v>4000</v>
+        <v>3999</v>
       </c>
       <c r="B407" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C407" t="s" s="1">
-        <v>4001</v>
+        <v>4000</v>
       </c>
       <c r="D407" t="s" s="2">
         <v>61</v>
@@ -67369,13 +67378,13 @@
     </row>
     <row r="408">
       <c r="A408" t="s" s="1">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="B408" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C408" t="s" s="1">
-        <v>4003</v>
+        <v>4002</v>
       </c>
       <c r="D408" t="s" s="2">
         <v>61</v>
@@ -67464,13 +67473,13 @@
     </row>
     <row r="409">
       <c r="A409" t="s" s="1">
-        <v>4004</v>
+        <v>4003</v>
       </c>
       <c r="B409" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C409" t="s" s="1">
-        <v>4005</v>
+        <v>4004</v>
       </c>
       <c r="D409" t="s" s="2">
         <v>61</v>
@@ -67559,13 +67568,13 @@
     </row>
     <row r="410">
       <c r="A410" t="s" s="1">
-        <v>4006</v>
+        <v>4005</v>
       </c>
       <c r="B410" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C410" t="s" s="1">
-        <v>4007</v>
+        <v>4006</v>
       </c>
       <c r="D410" t="s" s="2">
         <v>61</v>
@@ -67654,13 +67663,13 @@
     </row>
     <row r="411">
       <c r="A411" t="s" s="1">
-        <v>4008</v>
+        <v>4007</v>
       </c>
       <c r="B411" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C411" t="s" s="1">
-        <v>4009</v>
+        <v>4008</v>
       </c>
       <c r="D411" t="s" s="2">
         <v>61</v>
@@ -67749,13 +67758,13 @@
     </row>
     <row r="412">
       <c r="A412" t="s" s="1">
-        <v>4010</v>
+        <v>4009</v>
       </c>
       <c r="B412" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C412" t="s" s="1">
-        <v>4011</v>
+        <v>4010</v>
       </c>
       <c r="D412" t="s" s="2">
         <v>61</v>
@@ -67844,13 +67853,13 @@
     </row>
     <row r="413">
       <c r="A413" t="s" s="1">
-        <v>4012</v>
+        <v>4011</v>
       </c>
       <c r="B413" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C413" t="s" s="1">
-        <v>4013</v>
+        <v>4012</v>
       </c>
       <c r="D413" t="s" s="2">
         <v>61</v>
@@ -67939,13 +67948,13 @@
     </row>
     <row r="414">
       <c r="A414" t="s" s="1">
-        <v>4014</v>
+        <v>4013</v>
       </c>
       <c r="B414" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C414" t="s" s="1">
-        <v>4015</v>
+        <v>4014</v>
       </c>
       <c r="D414" t="s" s="2">
         <v>61</v>
@@ -68034,13 +68043,13 @@
     </row>
     <row r="415">
       <c r="A415" t="s" s="1">
-        <v>4016</v>
+        <v>4015</v>
       </c>
       <c r="B415" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C415" t="s" s="1">
-        <v>4017</v>
+        <v>4016</v>
       </c>
       <c r="D415" t="s" s="2">
         <v>61</v>
@@ -68129,13 +68138,13 @@
     </row>
     <row r="416">
       <c r="A416" t="s" s="1">
-        <v>4018</v>
+        <v>4017</v>
       </c>
       <c r="B416" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C416" t="s" s="1">
-        <v>2669</v>
+        <v>4018</v>
       </c>
       <c r="D416" t="s" s="2">
         <v>61</v>
@@ -68325,7 +68334,7 @@
         <v>32</v>
       </c>
       <c r="C418" t="s" s="1">
-        <v>4022</v>
+        <v>2669</v>
       </c>
       <c r="D418" t="s" s="2">
         <v>61</v>
@@ -68414,13 +68423,13 @@
     </row>
     <row r="419">
       <c r="A419" t="s" s="1">
-        <v>4023</v>
+        <v>4022</v>
       </c>
       <c r="B419" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C419" t="s" s="1">
-        <v>4024</v>
+        <v>4023</v>
       </c>
       <c r="D419" t="s" s="2">
         <v>61</v>
@@ -68509,13 +68518,13 @@
     </row>
     <row r="420">
       <c r="A420" t="s" s="1">
-        <v>4025</v>
+        <v>4024</v>
       </c>
       <c r="B420" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C420" t="s" s="1">
-        <v>4026</v>
+        <v>4025</v>
       </c>
       <c r="D420" t="s" s="2">
         <v>61</v>
@@ -68604,13 +68613,13 @@
     </row>
     <row r="421">
       <c r="A421" t="s" s="1">
-        <v>4027</v>
+        <v>4026</v>
       </c>
       <c r="B421" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C421" t="s" s="1">
-        <v>4028</v>
+        <v>4027</v>
       </c>
       <c r="D421" t="s" s="2">
         <v>61</v>
@@ -68699,13 +68708,13 @@
     </row>
     <row r="422">
       <c r="A422" t="s" s="1">
-        <v>4029</v>
+        <v>4028</v>
       </c>
       <c r="B422" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C422" t="s" s="1">
-        <v>4030</v>
+        <v>4029</v>
       </c>
       <c r="D422" t="s" s="2">
         <v>61</v>
@@ -68794,13 +68803,13 @@
     </row>
     <row r="423">
       <c r="A423" t="s" s="1">
-        <v>4031</v>
+        <v>4030</v>
       </c>
       <c r="B423" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C423" t="s" s="1">
-        <v>4032</v>
+        <v>4031</v>
       </c>
       <c r="D423" t="s" s="2">
         <v>61</v>
@@ -68889,13 +68898,13 @@
     </row>
     <row r="424">
       <c r="A424" t="s" s="1">
-        <v>4033</v>
+        <v>4032</v>
       </c>
       <c r="B424" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C424" t="s" s="1">
-        <v>4034</v>
+        <v>4033</v>
       </c>
       <c r="D424" t="s" s="2">
         <v>61</v>
@@ -68984,13 +68993,13 @@
     </row>
     <row r="425">
       <c r="A425" t="s" s="1">
-        <v>4035</v>
+        <v>4034</v>
       </c>
       <c r="B425" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C425" t="s" s="1">
-        <v>4036</v>
+        <v>4035</v>
       </c>
       <c r="D425" t="s" s="2">
         <v>61</v>
@@ -69079,13 +69088,13 @@
     </row>
     <row r="426">
       <c r="A426" t="s" s="1">
-        <v>4037</v>
+        <v>4036</v>
       </c>
       <c r="B426" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C426" t="s" s="1">
-        <v>4038</v>
+        <v>4037</v>
       </c>
       <c r="D426" t="s" s="2">
         <v>61</v>
@@ -69174,13 +69183,13 @@
     </row>
     <row r="427">
       <c r="A427" t="s" s="1">
-        <v>4039</v>
+        <v>4038</v>
       </c>
       <c r="B427" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C427" t="s" s="1">
-        <v>4040</v>
+        <v>4039</v>
       </c>
       <c r="D427" t="s" s="2">
         <v>61</v>
@@ -69269,13 +69278,13 @@
     </row>
     <row r="428">
       <c r="A428" t="s" s="1">
-        <v>4041</v>
+        <v>4040</v>
       </c>
       <c r="B428" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C428" t="s" s="1">
-        <v>4042</v>
+        <v>4041</v>
       </c>
       <c r="D428" t="s" s="2">
         <v>61</v>
@@ -69364,13 +69373,13 @@
     </row>
     <row r="429">
       <c r="A429" t="s" s="1">
-        <v>4043</v>
+        <v>4042</v>
       </c>
       <c r="B429" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C429" t="s" s="1">
-        <v>4044</v>
+        <v>4043</v>
       </c>
       <c r="D429" t="s" s="2">
         <v>61</v>
@@ -69459,13 +69468,13 @@
     </row>
     <row r="430">
       <c r="A430" t="s" s="1">
-        <v>4045</v>
+        <v>4044</v>
       </c>
       <c r="B430" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C430" t="s" s="1">
-        <v>4046</v>
+        <v>4045</v>
       </c>
       <c r="D430" t="s" s="2">
         <v>61</v>
@@ -69554,13 +69563,13 @@
     </row>
     <row r="431">
       <c r="A431" t="s" s="1">
-        <v>4047</v>
+        <v>4046</v>
       </c>
       <c r="B431" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C431" t="s" s="1">
-        <v>4048</v>
+        <v>4047</v>
       </c>
       <c r="D431" t="s" s="2">
         <v>61</v>
@@ -69649,108 +69658,108 @@
     </row>
     <row r="432">
       <c r="A432" t="s" s="1">
-        <v>4049</v>
+        <v>4048</v>
       </c>
       <c r="B432" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C432" t="s" s="1">
-        <v>2714</v>
-      </c>
-      <c r="D432" t="s" s="1">
-        <v>4050</v>
-      </c>
-      <c r="E432" t="s" s="1">
-        <v>4051</v>
-      </c>
-      <c r="F432" t="s" s="1">
-        <v>2714</v>
-      </c>
-      <c r="G432" t="s" s="1">
-        <v>4052</v>
-      </c>
-      <c r="H432" t="s" s="1">
-        <v>4053</v>
-      </c>
-      <c r="I432" t="s" s="1">
-        <v>4050</v>
-      </c>
-      <c r="J432" t="s" s="1">
-        <v>2714</v>
-      </c>
-      <c r="K432" t="s" s="1">
-        <v>4054</v>
-      </c>
-      <c r="L432" t="s" s="1">
-        <v>2713</v>
-      </c>
-      <c r="M432" t="s" s="1">
-        <v>4050</v>
-      </c>
-      <c r="N432" t="s" s="1">
-        <v>2715</v>
-      </c>
-      <c r="O432" t="s" s="1">
-        <v>3537</v>
-      </c>
-      <c r="P432" t="s" s="1">
-        <v>2719</v>
-      </c>
-      <c r="Q432" t="s" s="1">
-        <v>4055</v>
-      </c>
-      <c r="R432" t="s" s="1">
-        <v>2719</v>
-      </c>
-      <c r="S432" t="s" s="1">
-        <v>4056</v>
-      </c>
-      <c r="T432" t="s" s="1">
-        <v>4050</v>
-      </c>
-      <c r="U432" t="s" s="1">
-        <v>4050</v>
-      </c>
-      <c r="V432" t="s" s="1">
-        <v>4057</v>
-      </c>
-      <c r="W432" t="s" s="1">
-        <v>4058</v>
-      </c>
-      <c r="X432" t="s" s="1">
-        <v>4051</v>
-      </c>
-      <c r="Y432" t="s" s="1">
-        <v>4059</v>
-      </c>
-      <c r="Z432" t="s" s="1">
-        <v>4060</v>
-      </c>
-      <c r="AA432" t="s" s="1">
-        <v>4061</v>
-      </c>
-      <c r="AB432" t="s" s="1">
-        <v>4062</v>
-      </c>
-      <c r="AC432" t="s" s="1">
-        <v>4063</v>
-      </c>
-      <c r="AD432" t="s" s="1">
-        <v>2728</v>
-      </c>
-      <c r="AE432" t="s" s="1">
-        <v>2729</v>
+        <v>4049</v>
+      </c>
+      <c r="D432" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="E432" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="F432" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="G432" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="H432" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="I432" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="J432" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="K432" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="L432" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="M432" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="N432" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="O432" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="P432" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="Q432" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="R432" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="S432" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="T432" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="U432" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="V432" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="W432" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="X432" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="Y432" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="Z432" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="AA432" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="AB432" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="AC432" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="AD432" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="AE432" t="s" s="2">
+        <v>61</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="s" s="1">
-        <v>4064</v>
+        <v>4050</v>
       </c>
       <c r="B433" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C433" t="s" s="1">
-        <v>4065</v>
+        <v>4051</v>
       </c>
       <c r="D433" t="s" s="2">
         <v>61</v>
@@ -69839,108 +69848,108 @@
     </row>
     <row r="434">
       <c r="A434" t="s" s="1">
-        <v>4066</v>
+        <v>4052</v>
       </c>
       <c r="B434" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C434" t="s" s="1">
-        <v>4067</v>
-      </c>
-      <c r="D434" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="E434" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="F434" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="G434" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="H434" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="I434" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="J434" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="K434" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="L434" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="M434" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="N434" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="O434" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="P434" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="Q434" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="R434" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="S434" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="T434" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="U434" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="V434" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="W434" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="X434" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="Y434" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="Z434" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="AA434" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="AB434" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="AC434" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="AD434" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="AE434" t="s" s="2">
-        <v>61</v>
+        <v>2714</v>
+      </c>
+      <c r="D434" t="s" s="1">
+        <v>4053</v>
+      </c>
+      <c r="E434" t="s" s="1">
+        <v>4054</v>
+      </c>
+      <c r="F434" t="s" s="1">
+        <v>2714</v>
+      </c>
+      <c r="G434" t="s" s="1">
+        <v>4055</v>
+      </c>
+      <c r="H434" t="s" s="1">
+        <v>4056</v>
+      </c>
+      <c r="I434" t="s" s="1">
+        <v>4053</v>
+      </c>
+      <c r="J434" t="s" s="1">
+        <v>2714</v>
+      </c>
+      <c r="K434" t="s" s="1">
+        <v>4057</v>
+      </c>
+      <c r="L434" t="s" s="1">
+        <v>2713</v>
+      </c>
+      <c r="M434" t="s" s="1">
+        <v>4053</v>
+      </c>
+      <c r="N434" t="s" s="1">
+        <v>2715</v>
+      </c>
+      <c r="O434" t="s" s="1">
+        <v>3537</v>
+      </c>
+      <c r="P434" t="s" s="1">
+        <v>2719</v>
+      </c>
+      <c r="Q434" t="s" s="1">
+        <v>4058</v>
+      </c>
+      <c r="R434" t="s" s="1">
+        <v>2719</v>
+      </c>
+      <c r="S434" t="s" s="1">
+        <v>4059</v>
+      </c>
+      <c r="T434" t="s" s="1">
+        <v>4053</v>
+      </c>
+      <c r="U434" t="s" s="1">
+        <v>4053</v>
+      </c>
+      <c r="V434" t="s" s="1">
+        <v>4060</v>
+      </c>
+      <c r="W434" t="s" s="1">
+        <v>4061</v>
+      </c>
+      <c r="X434" t="s" s="1">
+        <v>4054</v>
+      </c>
+      <c r="Y434" t="s" s="1">
+        <v>4062</v>
+      </c>
+      <c r="Z434" t="s" s="1">
+        <v>4063</v>
+      </c>
+      <c r="AA434" t="s" s="1">
+        <v>4064</v>
+      </c>
+      <c r="AB434" t="s" s="1">
+        <v>4065</v>
+      </c>
+      <c r="AC434" t="s" s="1">
+        <v>4066</v>
+      </c>
+      <c r="AD434" t="s" s="1">
+        <v>2728</v>
+      </c>
+      <c r="AE434" t="s" s="1">
+        <v>2729</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="s" s="1">
-        <v>4068</v>
+        <v>4067</v>
       </c>
       <c r="B435" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C435" t="s" s="1">
-        <v>4069</v>
+        <v>4068</v>
       </c>
       <c r="D435" t="s" s="2">
         <v>61</v>
@@ -70029,13 +70038,13 @@
     </row>
     <row r="436">
       <c r="A436" t="s" s="1">
-        <v>4070</v>
+        <v>4069</v>
       </c>
       <c r="B436" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C436" t="s" s="1">
-        <v>4071</v>
+        <v>4070</v>
       </c>
       <c r="D436" t="s" s="2">
         <v>61</v>
@@ -70124,13 +70133,13 @@
     </row>
     <row r="437">
       <c r="A437" t="s" s="1">
-        <v>4072</v>
+        <v>4071</v>
       </c>
       <c r="B437" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C437" t="s" s="1">
-        <v>4073</v>
+        <v>4072</v>
       </c>
       <c r="D437" t="s" s="2">
         <v>61</v>
@@ -70219,13 +70228,13 @@
     </row>
     <row r="438">
       <c r="A438" t="s" s="1">
-        <v>4074</v>
+        <v>4073</v>
       </c>
       <c r="B438" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C438" t="s" s="1">
-        <v>4075</v>
+        <v>4074</v>
       </c>
       <c r="D438" t="s" s="2">
         <v>61</v>
@@ -70314,13 +70323,13 @@
     </row>
     <row r="439">
       <c r="A439" t="s" s="1">
-        <v>4076</v>
+        <v>4075</v>
       </c>
       <c r="B439" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C439" t="s" s="1">
-        <v>4077</v>
+        <v>4076</v>
       </c>
       <c r="D439" t="s" s="2">
         <v>61</v>
@@ -70409,13 +70418,13 @@
     </row>
     <row r="440">
       <c r="A440" t="s" s="1">
-        <v>4078</v>
+        <v>4077</v>
       </c>
       <c r="B440" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C440" t="s" s="1">
-        <v>4079</v>
+        <v>4078</v>
       </c>
       <c r="D440" t="s" s="2">
         <v>61</v>
@@ -70504,13 +70513,13 @@
     </row>
     <row r="441">
       <c r="A441" t="s" s="1">
-        <v>4080</v>
+        <v>4079</v>
       </c>
       <c r="B441" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C441" t="s" s="1">
-        <v>4081</v>
+        <v>4080</v>
       </c>
       <c r="D441" t="s" s="2">
         <v>61</v>
@@ -70599,13 +70608,13 @@
     </row>
     <row r="442">
       <c r="A442" t="s" s="1">
-        <v>4082</v>
+        <v>4081</v>
       </c>
       <c r="B442" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C442" t="s" s="1">
-        <v>4083</v>
+        <v>4082</v>
       </c>
       <c r="D442" t="s" s="2">
         <v>61</v>
@@ -70694,13 +70703,13 @@
     </row>
     <row r="443">
       <c r="A443" t="s" s="1">
-        <v>4084</v>
+        <v>4083</v>
       </c>
       <c r="B443" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C443" t="s" s="1">
-        <v>4085</v>
+        <v>4084</v>
       </c>
       <c r="D443" t="s" s="2">
         <v>61</v>
@@ -70789,13 +70798,13 @@
     </row>
     <row r="444">
       <c r="A444" t="s" s="1">
-        <v>4086</v>
+        <v>4085</v>
       </c>
       <c r="B444" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C444" t="s" s="1">
-        <v>4087</v>
+        <v>4086</v>
       </c>
       <c r="D444" t="s" s="2">
         <v>61</v>
@@ -70884,13 +70893,13 @@
     </row>
     <row r="445">
       <c r="A445" t="s" s="1">
-        <v>4088</v>
+        <v>4087</v>
       </c>
       <c r="B445" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C445" t="s" s="1">
-        <v>4089</v>
+        <v>4088</v>
       </c>
       <c r="D445" t="s" s="2">
         <v>61</v>
@@ -70979,13 +70988,13 @@
     </row>
     <row r="446">
       <c r="A446" t="s" s="1">
-        <v>4090</v>
+        <v>4089</v>
       </c>
       <c r="B446" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C446" t="s" s="1">
-        <v>4091</v>
+        <v>4090</v>
       </c>
       <c r="D446" t="s" s="2">
         <v>61</v>
@@ -71074,13 +71083,13 @@
     </row>
     <row r="447">
       <c r="A447" t="s" s="1">
-        <v>4092</v>
+        <v>4091</v>
       </c>
       <c r="B447" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C447" t="s" s="1">
-        <v>4093</v>
+        <v>4092</v>
       </c>
       <c r="D447" t="s" s="2">
         <v>61</v>
@@ -71169,13 +71178,13 @@
     </row>
     <row r="448">
       <c r="A448" t="s" s="1">
-        <v>4094</v>
+        <v>4093</v>
       </c>
       <c r="B448" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C448" t="s" s="1">
-        <v>0</v>
+        <v>4094</v>
       </c>
       <c r="D448" t="s" s="2">
         <v>61</v>
@@ -71365,7 +71374,7 @@
         <v>32</v>
       </c>
       <c r="C450" t="s" s="1">
-        <v>4098</v>
+        <v>0</v>
       </c>
       <c r="D450" t="s" s="2">
         <v>61</v>
@@ -71454,13 +71463,13 @@
     </row>
     <row r="451">
       <c r="A451" t="s" s="1">
-        <v>4099</v>
+        <v>4098</v>
       </c>
       <c r="B451" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C451" t="s" s="1">
-        <v>4100</v>
+        <v>4099</v>
       </c>
       <c r="D451" t="s" s="2">
         <v>61</v>
@@ -71549,13 +71558,13 @@
     </row>
     <row r="452">
       <c r="A452" t="s" s="1">
-        <v>4101</v>
+        <v>4100</v>
       </c>
       <c r="B452" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C452" t="s" s="1">
-        <v>4102</v>
+        <v>4101</v>
       </c>
       <c r="D452" t="s" s="2">
         <v>61</v>
@@ -71644,13 +71653,13 @@
     </row>
     <row r="453">
       <c r="A453" t="s" s="1">
-        <v>4103</v>
+        <v>4102</v>
       </c>
       <c r="B453" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C453" t="s" s="1">
-        <v>4104</v>
+        <v>4103</v>
       </c>
       <c r="D453" t="s" s="2">
         <v>61</v>
@@ -71739,13 +71748,13 @@
     </row>
     <row r="454">
       <c r="A454" t="s" s="1">
-        <v>4105</v>
+        <v>4104</v>
       </c>
       <c r="B454" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C454" t="s" s="1">
-        <v>4106</v>
+        <v>4105</v>
       </c>
       <c r="D454" t="s" s="2">
         <v>61</v>
@@ -71834,13 +71843,13 @@
     </row>
     <row r="455">
       <c r="A455" t="s" s="1">
-        <v>4107</v>
+        <v>4106</v>
       </c>
       <c r="B455" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C455" t="s" s="1">
-        <v>4108</v>
+        <v>4107</v>
       </c>
       <c r="D455" t="s" s="2">
         <v>61</v>
@@ -71929,13 +71938,13 @@
     </row>
     <row r="456">
       <c r="A456" t="s" s="1">
-        <v>4109</v>
+        <v>4108</v>
       </c>
       <c r="B456" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C456" t="s" s="1">
-        <v>4110</v>
+        <v>4109</v>
       </c>
       <c r="D456" t="s" s="2">
         <v>61</v>
@@ -72024,13 +72033,13 @@
     </row>
     <row r="457">
       <c r="A457" t="s" s="1">
-        <v>4111</v>
+        <v>4110</v>
       </c>
       <c r="B457" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C457" t="s" s="1">
-        <v>4112</v>
+        <v>4111</v>
       </c>
       <c r="D457" t="s" s="2">
         <v>61</v>
@@ -72119,13 +72128,13 @@
     </row>
     <row r="458">
       <c r="A458" t="s" s="1">
-        <v>4113</v>
+        <v>4112</v>
       </c>
       <c r="B458" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C458" t="s" s="1">
-        <v>4114</v>
+        <v>4113</v>
       </c>
       <c r="D458" t="s" s="2">
         <v>61</v>
@@ -72214,13 +72223,13 @@
     </row>
     <row r="459">
       <c r="A459" t="s" s="1">
-        <v>4115</v>
+        <v>4114</v>
       </c>
       <c r="B459" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C459" t="s" s="1">
-        <v>4116</v>
+        <v>4115</v>
       </c>
       <c r="D459" t="s" s="2">
         <v>61</v>
@@ -72309,13 +72318,13 @@
     </row>
     <row r="460">
       <c r="A460" t="s" s="1">
-        <v>4117</v>
+        <v>4116</v>
       </c>
       <c r="B460" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C460" t="s" s="1">
-        <v>4118</v>
+        <v>4117</v>
       </c>
       <c r="D460" t="s" s="2">
         <v>61</v>
@@ -72404,13 +72413,13 @@
     </row>
     <row r="461">
       <c r="A461" t="s" s="1">
-        <v>4119</v>
+        <v>4118</v>
       </c>
       <c r="B461" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C461" t="s" s="1">
-        <v>4120</v>
+        <v>4119</v>
       </c>
       <c r="D461" t="s" s="2">
         <v>61</v>
@@ -72499,13 +72508,13 @@
     </row>
     <row r="462">
       <c r="A462" t="s" s="1">
-        <v>4121</v>
+        <v>4120</v>
       </c>
       <c r="B462" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C462" t="s" s="1">
-        <v>4122</v>
+        <v>4121</v>
       </c>
       <c r="D462" t="s" s="2">
         <v>61</v>
@@ -72594,13 +72603,13 @@
     </row>
     <row r="463">
       <c r="A463" t="s" s="1">
-        <v>4123</v>
+        <v>4122</v>
       </c>
       <c r="B463" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C463" t="s" s="1">
-        <v>4081</v>
+        <v>4123</v>
       </c>
       <c r="D463" t="s" s="2">
         <v>61</v>
@@ -72695,7 +72704,7 @@
         <v>32</v>
       </c>
       <c r="C464" t="s" s="1">
-        <v>4124</v>
+        <v>4125</v>
       </c>
       <c r="D464" t="s" s="2">
         <v>61</v>
@@ -72784,13 +72793,13 @@
     </row>
     <row r="465">
       <c r="A465" t="s" s="1">
-        <v>4125</v>
+        <v>4126</v>
       </c>
       <c r="B465" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C465" t="s" s="1">
-        <v>4081</v>
+        <v>4084</v>
       </c>
       <c r="D465" t="s" s="2">
         <v>61</v>
@@ -72879,7 +72888,7 @@
     </row>
     <row r="466">
       <c r="A466" t="s" s="1">
-        <v>4126</v>
+        <v>4127</v>
       </c>
       <c r="B466" t="s" s="1">
         <v>32</v>
@@ -72980,7 +72989,7 @@
         <v>32</v>
       </c>
       <c r="C467" t="s" s="1">
-        <v>4129</v>
+        <v>4084</v>
       </c>
       <c r="D467" t="s" s="2">
         <v>61</v>
@@ -73069,13 +73078,13 @@
     </row>
     <row r="468">
       <c r="A468" t="s" s="1">
-        <v>4130</v>
+        <v>4129</v>
       </c>
       <c r="B468" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C468" t="s" s="1">
-        <v>4131</v>
+        <v>4130</v>
       </c>
       <c r="D468" t="s" s="2">
         <v>61</v>
@@ -73164,13 +73173,13 @@
     </row>
     <row r="469">
       <c r="A469" t="s" s="1">
-        <v>4132</v>
+        <v>4131</v>
       </c>
       <c r="B469" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C469" t="s" s="1">
-        <v>4133</v>
+        <v>4132</v>
       </c>
       <c r="D469" t="s" s="2">
         <v>61</v>
@@ -73259,13 +73268,13 @@
     </row>
     <row r="470">
       <c r="A470" t="s" s="1">
-        <v>4134</v>
+        <v>4133</v>
       </c>
       <c r="B470" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C470" t="s" s="1">
-        <v>4135</v>
+        <v>4134</v>
       </c>
       <c r="D470" t="s" s="2">
         <v>61</v>
@@ -73354,13 +73363,13 @@
     </row>
     <row r="471">
       <c r="A471" t="s" s="1">
-        <v>4136</v>
+        <v>4135</v>
       </c>
       <c r="B471" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C471" t="s" s="1">
-        <v>4137</v>
+        <v>4136</v>
       </c>
       <c r="D471" t="s" s="2">
         <v>61</v>
@@ -73449,13 +73458,13 @@
     </row>
     <row r="472">
       <c r="A472" t="s" s="1">
-        <v>4138</v>
+        <v>4137</v>
       </c>
       <c r="B472" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C472" t="s" s="1">
-        <v>4139</v>
+        <v>4138</v>
       </c>
       <c r="D472" t="s" s="2">
         <v>61</v>
@@ -73544,13 +73553,13 @@
     </row>
     <row r="473">
       <c r="A473" t="s" s="1">
-        <v>4140</v>
+        <v>4139</v>
       </c>
       <c r="B473" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C473" t="s" s="1">
-        <v>4081</v>
+        <v>4140</v>
       </c>
       <c r="D473" t="s" s="2">
         <v>61</v>
@@ -73740,7 +73749,7 @@
         <v>32</v>
       </c>
       <c r="C475" t="s" s="1">
-        <v>4144</v>
+        <v>4084</v>
       </c>
       <c r="D475" t="s" s="2">
         <v>61</v>
@@ -73829,13 +73838,13 @@
     </row>
     <row r="476">
       <c r="A476" t="s" s="1">
-        <v>4145</v>
+        <v>4144</v>
       </c>
       <c r="B476" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C476" t="s" s="1">
-        <v>4146</v>
+        <v>4145</v>
       </c>
       <c r="D476" t="s" s="2">
         <v>61</v>
@@ -73924,13 +73933,13 @@
     </row>
     <row r="477">
       <c r="A477" t="s" s="1">
-        <v>4147</v>
+        <v>4146</v>
       </c>
       <c r="B477" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C477" t="s" s="1">
-        <v>4148</v>
+        <v>4147</v>
       </c>
       <c r="D477" t="s" s="2">
         <v>61</v>
@@ -74019,13 +74028,13 @@
     </row>
     <row r="478">
       <c r="A478" t="s" s="1">
-        <v>4149</v>
+        <v>4148</v>
       </c>
       <c r="B478" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C478" t="s" s="1">
-        <v>4150</v>
+        <v>4149</v>
       </c>
       <c r="D478" t="s" s="2">
         <v>61</v>
@@ -74114,13 +74123,13 @@
     </row>
     <row r="479">
       <c r="A479" t="s" s="1">
-        <v>4151</v>
+        <v>4150</v>
       </c>
       <c r="B479" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C479" t="s" s="1">
-        <v>4152</v>
+        <v>4151</v>
       </c>
       <c r="D479" t="s" s="2">
         <v>61</v>
@@ -74209,13 +74218,13 @@
     </row>
     <row r="480">
       <c r="A480" t="s" s="1">
-        <v>4153</v>
+        <v>4152</v>
       </c>
       <c r="B480" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C480" t="s" s="1">
-        <v>4154</v>
+        <v>4153</v>
       </c>
       <c r="D480" t="s" s="2">
         <v>61</v>
@@ -74304,13 +74313,13 @@
     </row>
     <row r="481">
       <c r="A481" t="s" s="1">
-        <v>4155</v>
+        <v>4154</v>
       </c>
       <c r="B481" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C481" t="s" s="1">
-        <v>4156</v>
+        <v>4155</v>
       </c>
       <c r="D481" t="s" s="2">
         <v>61</v>
@@ -74399,13 +74408,13 @@
     </row>
     <row r="482">
       <c r="A482" t="s" s="1">
-        <v>4157</v>
+        <v>4156</v>
       </c>
       <c r="B482" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C482" t="s" s="1">
-        <v>4158</v>
+        <v>4157</v>
       </c>
       <c r="D482" t="s" s="2">
         <v>61</v>
@@ -74494,13 +74503,13 @@
     </row>
     <row r="483">
       <c r="A483" t="s" s="1">
-        <v>4159</v>
+        <v>4158</v>
       </c>
       <c r="B483" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C483" t="s" s="1">
-        <v>4160</v>
+        <v>4159</v>
       </c>
       <c r="D483" t="s" s="2">
         <v>61</v>
@@ -74589,13 +74598,13 @@
     </row>
     <row r="484">
       <c r="A484" t="s" s="1">
-        <v>4161</v>
+        <v>4160</v>
       </c>
       <c r="B484" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C484" t="s" s="1">
-        <v>4162</v>
+        <v>4161</v>
       </c>
       <c r="D484" t="s" s="2">
         <v>61</v>
@@ -74684,13 +74693,13 @@
     </row>
     <row r="485">
       <c r="A485" t="s" s="1">
-        <v>4163</v>
+        <v>4162</v>
       </c>
       <c r="B485" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C485" t="s" s="1">
-        <v>4164</v>
+        <v>4163</v>
       </c>
       <c r="D485" t="s" s="2">
         <v>61</v>
@@ -74779,13 +74788,13 @@
     </row>
     <row r="486">
       <c r="A486" t="s" s="1">
-        <v>4165</v>
+        <v>4164</v>
       </c>
       <c r="B486" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C486" t="s" s="1">
-        <v>4166</v>
+        <v>4165</v>
       </c>
       <c r="D486" t="s" s="2">
         <v>61</v>
@@ -74874,13 +74883,13 @@
     </row>
     <row r="487">
       <c r="A487" t="s" s="1">
-        <v>4167</v>
+        <v>4166</v>
       </c>
       <c r="B487" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C487" t="s" s="1">
-        <v>4168</v>
+        <v>4167</v>
       </c>
       <c r="D487" t="s" s="2">
         <v>61</v>
@@ -74969,13 +74978,13 @@
     </row>
     <row r="488">
       <c r="A488" t="s" s="1">
-        <v>4169</v>
+        <v>4168</v>
       </c>
       <c r="B488" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C488" t="s" s="1">
-        <v>3600</v>
+        <v>4169</v>
       </c>
       <c r="D488" t="s" s="2">
         <v>61</v>
@@ -75165,7 +75174,7 @@
         <v>32</v>
       </c>
       <c r="C490" t="s" s="1">
-        <v>4173</v>
+        <v>3600</v>
       </c>
       <c r="D490" t="s" s="2">
         <v>61</v>
@@ -75254,191 +75263,191 @@
     </row>
     <row r="491">
       <c r="A491" t="s" s="1">
-        <v>4174</v>
+        <v>4173</v>
       </c>
       <c r="B491" t="s" s="1">
         <v>32</v>
       </c>
       <c r="C491" t="s" s="1">
+        <v>4174</v>
+      </c>
+      <c r="D491" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="E491" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="F491" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="G491" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="H491" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="I491" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="J491" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="K491" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="L491" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="M491" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="N491" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="O491" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="P491" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="Q491" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="R491" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="S491" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="T491" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="U491" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="V491" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="W491" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="X491" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="Y491" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="Z491" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="AA491" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="AB491" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="AC491" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="AD491" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="AE491" t="s" s="2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="s" s="1">
         <v>4175</v>
       </c>
-      <c r="D491" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="E491" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="F491" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="G491" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="H491" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="I491" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="J491" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="K491" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="L491" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="M491" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="N491" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="O491" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="P491" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="Q491" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="R491" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="S491" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="T491" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="U491" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="V491" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="W491" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="X491" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="Y491" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="Z491" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="AA491" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="AB491" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="AC491" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="AD491" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="AE491" t="s" s="2">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="492" hidden="true">
-      <c r="A492" t="s" s="4">
+      <c r="B492" t="s" s="1">
+        <v>32</v>
+      </c>
+      <c r="C492" t="s" s="1">
         <v>4176</v>
       </c>
-      <c r="B492" t="s" s="4">
-        <v>199</v>
-      </c>
-      <c r="C492" t="s" s="4">
-        <v>4176</v>
-      </c>
-      <c r="D492" t="s" s="4">
-        <v>61</v>
-      </c>
-      <c r="E492" t="s" s="4">
-        <v>61</v>
-      </c>
-      <c r="F492" t="s" s="4">
-        <v>61</v>
-      </c>
-      <c r="G492" t="s" s="4">
-        <v>61</v>
-      </c>
-      <c r="H492" t="s" s="4">
-        <v>61</v>
-      </c>
-      <c r="I492" t="s" s="4">
-        <v>61</v>
-      </c>
-      <c r="J492" t="s" s="4">
-        <v>61</v>
-      </c>
-      <c r="K492" t="s" s="4">
-        <v>61</v>
-      </c>
-      <c r="L492" t="s" s="4">
-        <v>61</v>
-      </c>
-      <c r="M492" t="s" s="4">
-        <v>61</v>
-      </c>
-      <c r="N492" t="s" s="4">
-        <v>61</v>
-      </c>
-      <c r="O492" t="s" s="4">
-        <v>61</v>
-      </c>
-      <c r="P492" t="s" s="4">
-        <v>61</v>
-      </c>
-      <c r="Q492" t="s" s="4">
-        <v>61</v>
-      </c>
-      <c r="R492" t="s" s="4">
-        <v>61</v>
-      </c>
-      <c r="S492" t="s" s="4">
-        <v>61</v>
-      </c>
-      <c r="T492" t="s" s="4">
-        <v>61</v>
-      </c>
-      <c r="U492" t="s" s="4">
-        <v>61</v>
-      </c>
-      <c r="V492" t="s" s="4">
-        <v>61</v>
-      </c>
-      <c r="W492" t="s" s="4">
-        <v>61</v>
-      </c>
-      <c r="X492" t="s" s="4">
-        <v>61</v>
-      </c>
-      <c r="Y492" t="s" s="4">
-        <v>61</v>
-      </c>
-      <c r="Z492" t="s" s="4">
-        <v>61</v>
-      </c>
-      <c r="AA492" t="s" s="4">
-        <v>61</v>
-      </c>
-      <c r="AB492" t="s" s="4">
-        <v>61</v>
-      </c>
-      <c r="AC492" t="s" s="4">
-        <v>61</v>
-      </c>
-      <c r="AD492" t="s" s="4">
-        <v>61</v>
-      </c>
-      <c r="AE492" t="s" s="4">
+      <c r="D492" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="E492" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="F492" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="G492" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="H492" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="I492" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="J492" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="K492" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="L492" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="M492" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="N492" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="O492" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="P492" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="Q492" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="R492" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="S492" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="T492" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="U492" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="V492" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="W492" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="X492" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="Y492" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="Z492" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="AA492" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="AB492" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="AC492" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="AD492" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="AE492" t="s" s="2">
         <v>61</v>
       </c>
     </row>
@@ -75537,8 +75546,198 @@
         <v>61</v>
       </c>
     </row>
+    <row r="494" hidden="true">
+      <c r="A494" t="s" s="4">
+        <v>4179</v>
+      </c>
+      <c r="B494" t="s" s="4">
+        <v>199</v>
+      </c>
+      <c r="C494" t="s" s="4">
+        <v>4179</v>
+      </c>
+      <c r="D494" t="s" s="4">
+        <v>61</v>
+      </c>
+      <c r="E494" t="s" s="4">
+        <v>61</v>
+      </c>
+      <c r="F494" t="s" s="4">
+        <v>61</v>
+      </c>
+      <c r="G494" t="s" s="4">
+        <v>61</v>
+      </c>
+      <c r="H494" t="s" s="4">
+        <v>61</v>
+      </c>
+      <c r="I494" t="s" s="4">
+        <v>61</v>
+      </c>
+      <c r="J494" t="s" s="4">
+        <v>61</v>
+      </c>
+      <c r="K494" t="s" s="4">
+        <v>61</v>
+      </c>
+      <c r="L494" t="s" s="4">
+        <v>61</v>
+      </c>
+      <c r="M494" t="s" s="4">
+        <v>61</v>
+      </c>
+      <c r="N494" t="s" s="4">
+        <v>61</v>
+      </c>
+      <c r="O494" t="s" s="4">
+        <v>61</v>
+      </c>
+      <c r="P494" t="s" s="4">
+        <v>61</v>
+      </c>
+      <c r="Q494" t="s" s="4">
+        <v>61</v>
+      </c>
+      <c r="R494" t="s" s="4">
+        <v>61</v>
+      </c>
+      <c r="S494" t="s" s="4">
+        <v>61</v>
+      </c>
+      <c r="T494" t="s" s="4">
+        <v>61</v>
+      </c>
+      <c r="U494" t="s" s="4">
+        <v>61</v>
+      </c>
+      <c r="V494" t="s" s="4">
+        <v>61</v>
+      </c>
+      <c r="W494" t="s" s="4">
+        <v>61</v>
+      </c>
+      <c r="X494" t="s" s="4">
+        <v>61</v>
+      </c>
+      <c r="Y494" t="s" s="4">
+        <v>61</v>
+      </c>
+      <c r="Z494" t="s" s="4">
+        <v>61</v>
+      </c>
+      <c r="AA494" t="s" s="4">
+        <v>61</v>
+      </c>
+      <c r="AB494" t="s" s="4">
+        <v>61</v>
+      </c>
+      <c r="AC494" t="s" s="4">
+        <v>61</v>
+      </c>
+      <c r="AD494" t="s" s="4">
+        <v>61</v>
+      </c>
+      <c r="AE494" t="s" s="4">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="s" s="1">
+        <v>4180</v>
+      </c>
+      <c r="B495" t="s" s="1">
+        <v>32</v>
+      </c>
+      <c r="C495" t="s" s="1">
+        <v>4181</v>
+      </c>
+      <c r="D495" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="E495" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="F495" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="G495" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="H495" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="I495" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="J495" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="K495" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="L495" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="M495" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="N495" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="O495" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="P495" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="Q495" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="R495" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="S495" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="T495" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="U495" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="V495" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="W495" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="X495" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="Y495" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="Z495" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="AA495" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="AB495" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="AC495" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="AD495" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="AE495" t="s" s="2">
+        <v>61</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AF493"/>
+  <autoFilter ref="A1:AF495"/>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <drawing r:id="rId1"/>
   <legacyDrawing r:id="rId3"/>
